--- a/doc/help_dialogs/Input_files/symbolic.xlsx
+++ b/doc/help_dialogs/Input_files/symbolic.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="9"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="Symbolic Variables" sheetId="1" state="visible" r:id="rId3"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="180">
   <si>
     <t xml:space="preserve">SYMBOLIC VARIABLES</t>
   </si>
@@ -536,6 +536,12 @@
   </si>
   <si>
     <t xml:space="preserve">Return 1 if the bit n of value x (interpreted as integer) is set, otherwise 0.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">round(x)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return the rounded value of x.</t>
   </si>
   <si>
     <t xml:space="preserve">MATHEMATICAL CONSTANTS</t>
@@ -636,7 +642,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -698,7 +704,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -759,8 +765,12 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -843,37 +853,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0e2841"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="e8e8e8"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
         <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="e97132"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196b24"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0f9ed5"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="a02b93"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4ea72e"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
         <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607d"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -1013,7 +1023,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C35"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.27"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="59.82"/>
@@ -1376,7 +1386,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="44.09"/>
   </cols>
@@ -1423,8 +1433,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:B19"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="23.18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="25.09"/>
@@ -1569,6 +1579,14 @@
       </c>
       <c r="B18" s="11" t="s">
         <v>167</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -1588,11 +1606,11 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1600,12 +1618,12 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>2.71828182845904</v>
@@ -1613,7 +1631,7 @@
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>3.14159265358979</v>
@@ -1636,16 +1654,16 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1658,18 +1676,18 @@
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -1689,7 +1707,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26.09"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="36.82"/>
@@ -1792,7 +1810,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -1832,7 +1850,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18.09"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.09"/>
@@ -1889,7 +1907,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -1945,7 +1963,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -2001,7 +2019,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -2074,7 +2092,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -2135,7 +2153,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -2179,8 +2197,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman"&amp;12&amp;KffffffPage &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
--- a/doc/help_dialogs/Input_files/symbolic.xlsx
+++ b/doc/help_dialogs/Input_files/symbolic.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="10"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="Symbolic Variables" sheetId="1" state="visible" r:id="rId3"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="178">
   <si>
     <t xml:space="preserve">SYMBOLIC VARIABLES</t>
   </si>
@@ -536,12 +536,6 @@
   </si>
   <si>
     <t xml:space="preserve">Return 1 if the bit n of value x (interpreted as integer) is set, otherwise 0.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">round(x)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Return the rounded value of x.</t>
   </si>
   <si>
     <t xml:space="preserve">MATHEMATICAL CONSTANTS</t>
@@ -642,7 +636,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -704,7 +698,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -765,12 +759,8 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -853,37 +843,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="0e2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="e8e8e8"/>
       </a:lt2>
       <a:accent1>
         <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="e97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="196b24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="0f9ed5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="a02b93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="4ea72e"/>
       </a:accent6>
       <a:hlink>
         <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="96607d"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -1023,7 +1013,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C35"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.27"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="59.82"/>
@@ -1386,7 +1376,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="44.09"/>
   </cols>
@@ -1433,8 +1423,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:B18"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="23.18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="25.09"/>
@@ -1579,14 +1569,6 @@
       </c>
       <c r="B18" s="11" t="s">
         <v>167</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="B19" s="16" t="s">
-        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -1606,11 +1588,11 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1618,12 +1600,12 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>2.71828182845904</v>
@@ -1631,7 +1613,7 @@
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>3.14159265358979</v>
@@ -1654,16 +1636,16 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1676,18 +1658,18 @@
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -1707,7 +1689,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26.09"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="36.82"/>
@@ -1810,7 +1792,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -1850,7 +1832,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18.09"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.09"/>
@@ -1907,7 +1889,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -1963,7 +1945,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -2019,7 +2001,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -2092,7 +2074,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -2153,7 +2135,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -2197,8 +2179,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>